--- a/artfynd/A 29821-2023 artfynd.xlsx
+++ b/artfynd/A 29821-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,112 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>LJN0003 NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129523793</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58265</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>606240</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6726858</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 29821-2023 artfynd.xlsx
+++ b/artfynd/A 29821-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129523793</v>
       </c>
       <c r="B3" t="n">
-        <v>58265</v>
+        <v>58268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29821-2023 artfynd.xlsx
+++ b/artfynd/A 29821-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129523793</v>
       </c>
       <c r="B3" t="n">
-        <v>58268</v>
+        <v>58273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29821-2023 artfynd.xlsx
+++ b/artfynd/A 29821-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129523793</v>
       </c>
       <c r="B3" t="n">
-        <v>58273</v>
+        <v>58274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29821-2023 artfynd.xlsx
+++ b/artfynd/A 29821-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119545806</v>
+        <v>129523793</v>
       </c>
       <c r="B2" t="n">
-        <v>57791</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,14 +711,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gävle västra - Forsbacka, Gstr</t>
+          <t>Bergslagsbanan, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606283</v>
+        <v>606240</v>
       </c>
       <c r="R2" t="n">
-        <v>6726876</v>
+        <v>6726858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,21 +770,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LJN0003 NVI</t>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129523793</v>
+        <v>119545806</v>
       </c>
       <c r="B3" t="n">
-        <v>58274</v>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,14 +817,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergslagsbanan, Gstr</t>
+          <t>Gävle västra - Forsbacka, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606240</v>
+        <v>606283</v>
       </c>
       <c r="R3" t="n">
-        <v>6726858</v>
+        <v>6726876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +876,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Sanna Pousar</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Bergslagsbanan fågelinventeringar C240036</t>
+          <t>LJN0003 NVI</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 29821-2023 artfynd.xlsx
+++ b/artfynd/A 29821-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523793</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>LJN0003 NVI</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119545806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>